--- a/development/rocksdb/self_rd_e6_string_key/saved01/structured_log_data.xlsx
+++ b/development/rocksdb/self_rd_e6_string_key/saved01/structured_log_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>all_time_ns_out</t>
+          <t>all_time_ns _out</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -497,33 +497,33 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12879464666</v>
+        <v>18164486729</v>
       </c>
       <c r="C2" t="n">
-        <v>8425113</v>
+        <v>8423066</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>17605987233</v>
+        <v>17102017041</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>245673380447</v>
+        <v>210422845042</v>
       </c>
       <c r="H2" t="n">
-        <v>1062469400551</v>
+        <v>761993921052</v>
       </c>
       <c r="I2" t="n">
-        <v>5712</v>
+        <v>6408</v>
       </c>
       <c r="J2" t="n">
-        <v>251.33</v>
+        <v>218.67</v>
       </c>
       <c r="K2" t="n">
-        <v>1045802</v>
+        <v>909902</v>
       </c>
       <c r="L2" t="n">
-        <v>45892204.33</v>
+        <v>39016683.67</v>
       </c>
     </row>
     <row r="3">
@@ -533,33 +533,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12297336255</v>
+        <v>16858653936</v>
       </c>
       <c r="C3" t="n">
-        <v>8454228</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
+        <v>8328319</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0002</v>
+      </c>
       <c r="E3" t="n">
-        <v>14309955401</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>14020459668</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.0026</v>
+      </c>
       <c r="G3" t="n">
-        <v>181235017879</v>
+        <v>158039837641</v>
       </c>
       <c r="H3" t="n">
-        <v>1002641836372</v>
+        <v>723729805245</v>
       </c>
       <c r="I3" t="n">
-        <v>1952</v>
+        <v>8256</v>
       </c>
       <c r="J3" t="n">
-        <v>251.33</v>
+        <v>218.67</v>
       </c>
       <c r="K3" t="n">
-        <v>1045802</v>
+        <v>909902</v>
       </c>
       <c r="L3" t="n">
-        <v>40908449.67</v>
+        <v>34717942.67</v>
       </c>
     </row>
     <row r="4">
@@ -569,33 +573,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12767939603</v>
+        <v>17266807228</v>
       </c>
       <c r="C4" t="n">
-        <v>8285162</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>8384938</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.0002</v>
+      </c>
       <c r="E4" t="n">
-        <v>14348379548</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>14231984606</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0026</v>
+      </c>
       <c r="G4" t="n">
-        <v>104613933049</v>
+        <v>83746497483</v>
       </c>
       <c r="H4" t="n">
-        <v>901654858599</v>
+        <v>638390792509</v>
       </c>
       <c r="I4" t="n">
-        <v>20096</v>
+        <v>42144</v>
       </c>
       <c r="J4" t="n">
-        <v>201</v>
+        <v>151.33</v>
       </c>
       <c r="K4" t="n">
-        <v>845392</v>
+        <v>633415</v>
       </c>
       <c r="L4" t="n">
-        <v>32544346</v>
+        <v>27877872.67</v>
       </c>
     </row>
     <row r="5">
@@ -605,33 +613,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12523971299</v>
+        <v>17763975846</v>
       </c>
       <c r="C5" t="n">
-        <v>8274266</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>8363938</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
       <c r="E5" t="n">
-        <v>14129586789</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>14170794603</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
       <c r="G5" t="n">
-        <v>704625082</v>
+        <v>160778982143</v>
       </c>
       <c r="H5" t="n">
-        <v>797268052269</v>
+        <v>708685101142</v>
       </c>
       <c r="I5" t="n">
-        <v>36640</v>
+        <v>4721</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>218.67</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>909902</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>39305067.33</v>
       </c>
     </row>
     <row r="6">
@@ -641,37 +653,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12335013048</v>
+        <v>17661141913</v>
       </c>
       <c r="C6" t="n">
-        <v>8277587</v>
+        <v>8387395</v>
       </c>
       <c r="D6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>14744927247</v>
+        <v>14211718034</v>
       </c>
       <c r="F6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>165865343881</v>
+        <v>99703755364</v>
       </c>
       <c r="H6" t="n">
-        <v>960389822283</v>
+        <v>649195827674</v>
       </c>
       <c r="I6" t="n">
-        <v>1715</v>
+        <v>19066</v>
       </c>
       <c r="J6" t="n">
-        <v>251.33</v>
+        <v>165</v>
       </c>
       <c r="K6" t="n">
-        <v>1045802</v>
+        <v>690586</v>
       </c>
       <c r="L6" t="n">
-        <v>43214462.67</v>
+        <v>30273697.67</v>
       </c>
     </row>
     <row r="7">
@@ -681,37 +693,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12541791454</v>
+        <v>17795342967</v>
       </c>
       <c r="C7" t="n">
-        <v>8303465</v>
+        <v>8290802</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="E7" t="n">
-        <v>14485543641</v>
+        <v>13960573322</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="G7" t="n">
-        <v>114030165477</v>
+        <v>156629611191</v>
       </c>
       <c r="H7" t="n">
-        <v>906147422424</v>
+        <v>702600997234</v>
       </c>
       <c r="I7" t="n">
-        <v>5517</v>
+        <v>1391</v>
       </c>
       <c r="J7" t="n">
-        <v>201</v>
+        <v>218.67</v>
       </c>
       <c r="K7" t="n">
-        <v>845392</v>
+        <v>909902</v>
       </c>
       <c r="L7" t="n">
-        <v>34430440.33</v>
+        <v>37435394.33</v>
       </c>
     </row>
     <row r="8">
@@ -721,37 +733,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12500496100</v>
+        <v>17764619127</v>
       </c>
       <c r="C8" t="n">
-        <v>8331880</v>
+        <v>8501659</v>
       </c>
       <c r="D8" t="n">
-        <v>-1</v>
+        <v>0.0008</v>
       </c>
       <c r="E8" t="n">
-        <v>14703804507</v>
+        <v>14409178452</v>
       </c>
       <c r="F8" t="n">
-        <v>-1</v>
+        <v>0.0022</v>
       </c>
       <c r="G8" t="n">
-        <v>186473681328</v>
+        <v>101804948453</v>
       </c>
       <c r="H8" t="n">
-        <v>980150629134</v>
+        <v>648681232947</v>
       </c>
       <c r="I8" t="n">
-        <v>1095</v>
+        <v>3719</v>
       </c>
       <c r="J8" t="n">
-        <v>251.33</v>
+        <v>165</v>
       </c>
       <c r="K8" t="n">
-        <v>1045802</v>
+        <v>690586</v>
       </c>
       <c r="L8" t="n">
-        <v>42311886.33</v>
+        <v>29149100.67</v>
       </c>
     </row>
     <row r="9">
@@ -761,37 +773,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12607784102</v>
+        <v>17912725681</v>
       </c>
       <c r="C9" t="n">
-        <v>8283382</v>
+        <v>8350941</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0013</v>
+        <v>0.0001</v>
       </c>
       <c r="E9" t="n">
-        <v>14110993365</v>
+        <v>14367439042</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0461</v>
+        <v>0.002</v>
       </c>
       <c r="G9" t="n">
-        <v>136234022800</v>
+        <v>167347297213</v>
       </c>
       <c r="H9" t="n">
-        <v>923282765467</v>
+        <v>716075957257</v>
       </c>
       <c r="I9" t="n">
-        <v>2276</v>
+        <v>2501</v>
       </c>
       <c r="J9" t="n">
-        <v>211.67</v>
+        <v>218.67</v>
       </c>
       <c r="K9" t="n">
-        <v>890225.33</v>
+        <v>909902</v>
       </c>
       <c r="L9" t="n">
-        <v>34780001.33</v>
+        <v>41016054</v>
       </c>
     </row>
     <row r="10">
@@ -801,37 +813,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12506096006</v>
+        <v>17520941774</v>
       </c>
       <c r="C10" t="n">
-        <v>8384435</v>
+        <v>8111314</v>
       </c>
       <c r="D10" t="n">
-        <v>-1</v>
+        <v>0.0008</v>
       </c>
       <c r="E10" t="n">
-        <v>14573769811</v>
+        <v>14243459704</v>
       </c>
       <c r="F10" t="n">
-        <v>-1</v>
+        <v>0.002</v>
       </c>
       <c r="G10" t="n">
-        <v>183629009484</v>
+        <v>101350924952</v>
       </c>
       <c r="H10" t="n">
-        <v>977469172218</v>
+        <v>651305193354</v>
       </c>
       <c r="I10" t="n">
-        <v>1405</v>
+        <v>8835</v>
       </c>
       <c r="J10" t="n">
-        <v>251.33</v>
+        <v>165</v>
       </c>
       <c r="K10" t="n">
-        <v>1045802</v>
+        <v>690586</v>
       </c>
       <c r="L10" t="n">
-        <v>43058450</v>
+        <v>27984107.67</v>
       </c>
     </row>
     <row r="11">
@@ -841,1190 +853,742 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12466822873</v>
+        <v>17669363236</v>
       </c>
       <c r="C11" t="n">
-        <v>8241820</v>
+        <v>8345645</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0011</v>
+        <v>0.0001</v>
       </c>
       <c r="E11" t="n">
-        <v>14646587666</v>
+        <v>14175620832</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0025</v>
+        <v>0.002</v>
       </c>
       <c r="G11" t="n">
-        <v>115071790804</v>
+        <v>163436727700</v>
       </c>
       <c r="H11" t="n">
-        <v>905723253204</v>
+        <v>706947250112</v>
       </c>
       <c r="I11" t="n">
-        <v>3974</v>
+        <v>3611</v>
       </c>
       <c r="J11" t="n">
-        <v>201</v>
+        <v>218.67</v>
       </c>
       <c r="K11" t="n">
-        <v>845392</v>
+        <v>909902</v>
       </c>
       <c r="L11" t="n">
-        <v>34505592.67</v>
+        <v>40954436</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>log6112</t>
+          <t>log7111</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12932703898</v>
+        <v>17670418783</v>
       </c>
       <c r="C12" t="n">
-        <v>8366267</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
+        <v>8338551</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.0008</v>
+      </c>
       <c r="E12" t="n">
-        <v>17684495316</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
+        <v>14194647689</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.002</v>
+      </c>
       <c r="G12" t="n">
-        <v>262002863756</v>
+        <v>99709069896</v>
       </c>
       <c r="H12" t="n">
-        <v>1073899830594</v>
+        <v>647788919270</v>
       </c>
       <c r="I12" t="n">
-        <v>5656</v>
+        <v>13950</v>
       </c>
       <c r="J12" t="n">
-        <v>340</v>
+        <v>165</v>
       </c>
       <c r="K12" t="n">
-        <v>1417078</v>
+        <v>690586</v>
       </c>
       <c r="L12" t="n">
-        <v>57173139.33</v>
+        <v>28791387</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>log6212</t>
+          <t>log7211</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12458594972</v>
+        <v>17588740317</v>
       </c>
       <c r="C13" t="n">
-        <v>8357102</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
+        <v>8395924</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.0001</v>
+      </c>
       <c r="E13" t="n">
-        <v>14818842392</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
+        <v>14239830121</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.002</v>
+      </c>
       <c r="G13" t="n">
-        <v>203955867517</v>
+        <v>166097926637</v>
       </c>
       <c r="H13" t="n">
-        <v>1026153676381</v>
+        <v>714116623681</v>
       </c>
       <c r="I13" t="n">
-        <v>1840</v>
+        <v>4443</v>
       </c>
       <c r="J13" t="n">
-        <v>340</v>
+        <v>218.67</v>
       </c>
       <c r="K13" t="n">
-        <v>1417078</v>
+        <v>909902</v>
       </c>
       <c r="L13" t="n">
-        <v>54697161.67</v>
+        <v>38420867</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>log6312</t>
+          <t>log7311</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12625159129</v>
+        <v>17533730719</v>
       </c>
       <c r="C14" t="n">
-        <v>8215847</v>
-      </c>
-      <c r="D14" t="inlineStr"/>
+        <v>8428258</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.0008</v>
+      </c>
       <c r="E14" t="n">
-        <v>14732394448</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
+        <v>14117036977</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.002</v>
+      </c>
       <c r="G14" t="n">
-        <v>124213346271</v>
+        <v>98452059990</v>
       </c>
       <c r="H14" t="n">
-        <v>923115012461</v>
+        <v>648033177815</v>
       </c>
       <c r="I14" t="n">
-        <v>37744</v>
+        <v>17787</v>
       </c>
       <c r="J14" t="n">
-        <v>285.33</v>
+        <v>165</v>
       </c>
       <c r="K14" t="n">
-        <v>1187296.67</v>
+        <v>690586</v>
       </c>
       <c r="L14" t="n">
-        <v>47930738.67</v>
+        <v>28245146</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>log6412</t>
+          <t>log7411</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12525213916</v>
+        <v>17605596131</v>
       </c>
       <c r="C15" t="n">
-        <v>8256363</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
+        <v>8335188</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.0001</v>
+      </c>
       <c r="E15" t="n">
-        <v>14335551518</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
+        <v>14363585556</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.002</v>
+      </c>
       <c r="G15" t="n">
-        <v>744377839</v>
+        <v>162543823687</v>
       </c>
       <c r="H15" t="n">
-        <v>798809040365</v>
+        <v>708718990156</v>
       </c>
       <c r="I15" t="n">
-        <v>72336</v>
+        <v>4443</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>218.67</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>909902</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>36593372.67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>log6512</t>
+          <t>log6112</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12504824156</v>
+        <v>18539299130</v>
       </c>
       <c r="C16" t="n">
-        <v>8303864</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-1</v>
-      </c>
+        <v>8329664</v>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>14379546458</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-1</v>
-      </c>
+        <v>16600809768</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>204074200825</v>
+        <v>212709019462</v>
       </c>
       <c r="H16" t="n">
-        <v>997303547471</v>
+        <v>762917866440</v>
       </c>
       <c r="I16" t="n">
-        <v>1822</v>
+        <v>8568</v>
       </c>
       <c r="J16" t="n">
-        <v>340</v>
+        <v>355.33</v>
       </c>
       <c r="K16" t="n">
-        <v>1417078</v>
+        <v>1464400.67</v>
       </c>
       <c r="L16" t="n">
-        <v>56279114.67</v>
+        <v>57564309.67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>log6612</t>
+          <t>log6212</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12695491025</v>
+        <v>17593628769</v>
       </c>
       <c r="C17" t="n">
-        <v>8293936</v>
+        <v>8411949</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="E17" t="n">
-        <v>14841014051</v>
+        <v>14247888382</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.0013</v>
       </c>
       <c r="G17" t="n">
-        <v>133188672547</v>
+        <v>172677103370</v>
       </c>
       <c r="H17" t="n">
-        <v>924919594629</v>
+        <v>736755813061</v>
       </c>
       <c r="I17" t="n">
-        <v>9091</v>
+        <v>8384</v>
       </c>
       <c r="J17" t="n">
-        <v>290.33</v>
+        <v>355.33</v>
       </c>
       <c r="K17" t="n">
-        <v>1208318.33</v>
+        <v>1464400.67</v>
       </c>
       <c r="L17" t="n">
-        <v>50760788</v>
+        <v>66003302.67</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>log6712</t>
+          <t>log6312</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12599648903</v>
+        <v>17842095537</v>
       </c>
       <c r="C18" t="n">
-        <v>8310289</v>
+        <v>8393490</v>
       </c>
       <c r="D18" t="n">
-        <v>-1</v>
+        <v>0.0001</v>
       </c>
       <c r="E18" t="n">
-        <v>14674095097</v>
+        <v>14303532586</v>
       </c>
       <c r="F18" t="n">
-        <v>-1</v>
+        <v>0.0013</v>
       </c>
       <c r="G18" t="n">
-        <v>207728720562</v>
+        <v>97663530862</v>
       </c>
       <c r="H18" t="n">
-        <v>1001068432122</v>
+        <v>653429938188</v>
       </c>
       <c r="I18" t="n">
-        <v>1164</v>
+        <v>89184</v>
       </c>
       <c r="J18" t="n">
-        <v>340</v>
+        <v>283.67</v>
       </c>
       <c r="K18" t="n">
-        <v>1417078</v>
+        <v>1172596.33</v>
       </c>
       <c r="L18" t="n">
-        <v>57562339</v>
+        <v>53192317.67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>log6812</t>
+          <t>log6412</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12502313757</v>
+        <v>17973991582</v>
       </c>
       <c r="C19" t="n">
-        <v>8309153</v>
+        <v>8400778</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0021</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>14743299928</v>
+        <v>13776869497</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0483</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>156403235045</v>
+        <v>168874361077</v>
       </c>
       <c r="H19" t="n">
-        <v>949956059138</v>
+        <v>716066564113</v>
       </c>
       <c r="I19" t="n">
-        <v>3574</v>
+        <v>5896</v>
       </c>
       <c r="J19" t="n">
-        <v>302.67</v>
+        <v>355.33</v>
       </c>
       <c r="K19" t="n">
-        <v>1260165.67</v>
+        <v>1464400.67</v>
       </c>
       <c r="L19" t="n">
-        <v>52313161</v>
+        <v>60301009.67</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>log6912</t>
+          <t>log6512</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12639717008</v>
+        <v>17997797904</v>
       </c>
       <c r="C20" t="n">
-        <v>8245992</v>
+        <v>8401686</v>
       </c>
       <c r="D20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>14859092592</v>
+        <v>13906225799</v>
       </c>
       <c r="F20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>207767672277</v>
+        <v>98249824274</v>
       </c>
       <c r="H20" t="n">
-        <v>1001849471913</v>
+        <v>646830137063</v>
       </c>
       <c r="I20" t="n">
-        <v>1494</v>
+        <v>40151</v>
       </c>
       <c r="J20" t="n">
-        <v>340</v>
+        <v>300</v>
       </c>
       <c r="K20" t="n">
-        <v>1417078</v>
+        <v>1240918</v>
       </c>
       <c r="L20" t="n">
-        <v>58857436.33</v>
+        <v>50507802.67</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>log7012</t>
+          <t>log6612</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12658598699</v>
+        <v>18171769907</v>
       </c>
       <c r="C21" t="n">
-        <v>8254224</v>
+        <v>8407176</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0019</v>
+        <v>0.0001</v>
       </c>
       <c r="E21" t="n">
-        <v>14920090934</v>
+        <v>14205322147</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0014</v>
+        <v>0.0011</v>
       </c>
       <c r="G21" t="n">
-        <v>134668184367</v>
+        <v>288230518628</v>
       </c>
       <c r="H21" t="n">
-        <v>926385823591</v>
+        <v>835048387261</v>
       </c>
       <c r="I21" t="n">
-        <v>6448</v>
+        <v>1726</v>
       </c>
       <c r="J21" t="n">
-        <v>290.33</v>
+        <v>355.33</v>
       </c>
       <c r="K21" t="n">
-        <v>1208318.33</v>
+        <v>1464400.67</v>
       </c>
       <c r="L21" t="n">
-        <v>49974312.67</v>
+        <v>60507200.33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>log6113</t>
+          <t>log6712</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13236733773</v>
+        <v>18008598087</v>
       </c>
       <c r="C22" t="n">
-        <v>8227978</v>
-      </c>
-      <c r="D22" t="inlineStr"/>
+        <v>8450447</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.0018</v>
+      </c>
       <c r="E22" t="n">
-        <v>17384830201</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
+        <v>14008663542</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.0014</v>
+      </c>
       <c r="G22" t="n">
-        <v>258599350624</v>
+        <v>100910069394</v>
       </c>
       <c r="H22" t="n">
-        <v>1066058087021</v>
+        <v>649020593301</v>
       </c>
       <c r="I22" t="n">
-        <v>7056</v>
+        <v>7333</v>
       </c>
       <c r="J22" t="n">
-        <v>226.33</v>
+        <v>300</v>
       </c>
       <c r="K22" t="n">
-        <v>946853.67</v>
+        <v>1240918</v>
       </c>
       <c r="L22" t="n">
-        <v>40140962.33</v>
+        <v>49303995.67</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>log6213</t>
+          <t>log6812</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12866760766</v>
+        <v>18400968695</v>
       </c>
       <c r="C23" t="n">
-        <v>8302350</v>
-      </c>
-      <c r="D23" t="inlineStr"/>
+        <v>8390336</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.0001</v>
+      </c>
       <c r="E23" t="n">
-        <v>14170528633</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
+        <v>13888181102</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.0011</v>
+      </c>
       <c r="G23" t="n">
-        <v>194557911572</v>
+        <v>168904545050</v>
       </c>
       <c r="H23" t="n">
-        <v>1014279109362</v>
+        <v>716237925251</v>
       </c>
       <c r="I23" t="n">
-        <v>2048</v>
+        <v>3116</v>
       </c>
       <c r="J23" t="n">
-        <v>226.33</v>
+        <v>355.33</v>
       </c>
       <c r="K23" t="n">
-        <v>946853.67</v>
+        <v>1464400.67</v>
       </c>
       <c r="L23" t="n">
-        <v>39148826.67</v>
+        <v>61684393</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>log6313</t>
+          <t>log6912</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>13176745697</v>
+        <v>17772749138</v>
       </c>
       <c r="C24" t="n">
-        <v>8301324</v>
-      </c>
-      <c r="D24" t="inlineStr"/>
+        <v>7963939</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.0018</v>
+      </c>
       <c r="E24" t="n">
-        <v>14222823684</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
+        <v>14003247394</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.0011</v>
+      </c>
       <c r="G24" t="n">
-        <v>100967784478</v>
+        <v>101872992693</v>
       </c>
       <c r="H24" t="n">
-        <v>896371501309</v>
+        <v>648937017622</v>
       </c>
       <c r="I24" t="n">
-        <v>64336</v>
+        <v>18271</v>
       </c>
       <c r="J24" t="n">
-        <v>187.33</v>
+        <v>300</v>
       </c>
       <c r="K24" t="n">
-        <v>784345.67</v>
+        <v>1240918</v>
       </c>
       <c r="L24" t="n">
-        <v>32119638.33</v>
+        <v>53724244.33</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>log6413</t>
+          <t>log7012</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>12697305852</v>
+        <v>18061783465</v>
       </c>
       <c r="C25" t="n">
-        <v>8362642</v>
-      </c>
-      <c r="D25" t="inlineStr"/>
+        <v>8364860</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.0001</v>
+      </c>
       <c r="E25" t="n">
-        <v>12824021439</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
+        <v>13885987419</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.0011</v>
+      </c>
       <c r="G25" t="n">
-        <v>717318708</v>
+        <v>170654362569</v>
       </c>
       <c r="H25" t="n">
-        <v>792980245273</v>
+        <v>717522474574</v>
       </c>
       <c r="I25" t="n">
-        <v>109392</v>
+        <v>4506</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>355.33</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1464400.67</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>62482681.33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>log6513</t>
+          <t>log7112</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>12884216537</v>
+        <v>18592040953</v>
       </c>
       <c r="C26" t="n">
-        <v>8296867</v>
+        <v>8388382</v>
       </c>
       <c r="D26" t="n">
-        <v>-1</v>
+        <v>0.0018</v>
       </c>
       <c r="E26" t="n">
-        <v>14316604403</v>
+        <v>13928296263</v>
       </c>
       <c r="F26" t="n">
-        <v>-1</v>
+        <v>0.0011</v>
       </c>
       <c r="G26" t="n">
-        <v>195846792939</v>
+        <v>99987604332</v>
       </c>
       <c r="H26" t="n">
-        <v>984367565255</v>
+        <v>641549110228</v>
       </c>
       <c r="I26" t="n">
-        <v>2324</v>
+        <v>29207</v>
       </c>
       <c r="J26" t="n">
-        <v>226.33</v>
+        <v>300</v>
       </c>
       <c r="K26" t="n">
-        <v>946853.67</v>
+        <v>1240918</v>
       </c>
       <c r="L26" t="n">
-        <v>37602832.67</v>
+        <v>49707102.33</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>log6613</t>
+          <t>log7212</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12919948135</v>
+        <v>17872554027</v>
       </c>
       <c r="C27" t="n">
-        <v>8273309</v>
+        <v>8314795</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="E27" t="n">
-        <v>14572327897</v>
+        <v>13888410319</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.0011</v>
       </c>
       <c r="G27" t="n">
-        <v>123964374676</v>
+        <v>168253408623</v>
       </c>
       <c r="H27" t="n">
-        <v>910845055027</v>
+        <v>715451221525</v>
       </c>
       <c r="I27" t="n">
-        <v>14630</v>
+        <v>5549</v>
       </c>
       <c r="J27" t="n">
-        <v>193</v>
+        <v>355.33</v>
       </c>
       <c r="K27" t="n">
-        <v>808156.67</v>
+        <v>1464400.67</v>
       </c>
       <c r="L27" t="n">
-        <v>32639338.67</v>
+        <v>61646665.33</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>log6713</t>
+          <t>log7312</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>12895738403</v>
+        <v>17948900172</v>
       </c>
       <c r="C28" t="n">
-        <v>8071639</v>
+        <v>8385969</v>
       </c>
       <c r="D28" t="n">
-        <v>-1</v>
+        <v>0.0018</v>
       </c>
       <c r="E28" t="n">
-        <v>14313805658</v>
+        <v>13862638236</v>
       </c>
       <c r="F28" t="n">
-        <v>-1</v>
+        <v>0.0011</v>
       </c>
       <c r="G28" t="n">
-        <v>200373160267</v>
+        <v>102180774256</v>
       </c>
       <c r="H28" t="n">
-        <v>989305693270</v>
+        <v>650104947016</v>
       </c>
       <c r="I28" t="n">
-        <v>1498</v>
+        <v>37416</v>
       </c>
       <c r="J28" t="n">
-        <v>226.33</v>
+        <v>300</v>
       </c>
       <c r="K28" t="n">
-        <v>946853.67</v>
+        <v>1240918</v>
       </c>
       <c r="L28" t="n">
-        <v>37077774.67</v>
+        <v>54318208.33</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>log6813</t>
+          <t>log7412</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>12913216701</v>
+        <v>18211590633</v>
       </c>
       <c r="C29" t="n">
-        <v>8159282</v>
+        <v>8357284</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0036</v>
+        <v>0.0001</v>
       </c>
       <c r="E29" t="n">
-        <v>14447539047</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.0506</v>
-      </c>
-      <c r="G29" t="n">
-        <v>148532129323</v>
-      </c>
-      <c r="H29" t="n">
-        <v>939020449110</v>
-      </c>
+        <v>13858262441</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>5569</v>
-      </c>
-      <c r="J29" t="n">
-        <v>202</v>
-      </c>
-      <c r="K29" t="n">
-        <v>845975.67</v>
-      </c>
-      <c r="L29" t="n">
-        <v>31615808</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>log6913</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>13077190234</v>
-      </c>
-      <c r="C30" t="n">
-        <v>8178279</v>
-      </c>
-      <c r="D30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E30" t="n">
-        <v>14417269322</v>
-      </c>
-      <c r="F30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G30" t="n">
-        <v>197838822643</v>
-      </c>
-      <c r="H30" t="n">
-        <v>987097151378</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1912</v>
-      </c>
-      <c r="J30" t="n">
-        <v>226.33</v>
-      </c>
-      <c r="K30" t="n">
-        <v>946853.67</v>
-      </c>
-      <c r="L30" t="n">
-        <v>40552377.33</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>log7013</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>13266969293</v>
-      </c>
-      <c r="C31" t="n">
-        <v>8187584</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.0035</v>
-      </c>
-      <c r="E31" t="n">
-        <v>14357278797</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="G31" t="n">
-        <v>125590096903</v>
-      </c>
-      <c r="H31" t="n">
-        <v>912135429958</v>
-      </c>
-      <c r="I31" t="n">
-        <v>10293</v>
-      </c>
-      <c r="J31" t="n">
-        <v>193</v>
-      </c>
-      <c r="K31" t="n">
-        <v>808156.67</v>
-      </c>
-      <c r="L31" t="n">
-        <v>32696248.67</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>log6114</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>13589279116</v>
-      </c>
-      <c r="C32" t="n">
-        <v>9421319</v>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="n">
-        <v>17446840709</v>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="n">
-        <v>263188543498</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1065876621959</v>
-      </c>
-      <c r="I32" t="n">
-        <v>6440</v>
-      </c>
-      <c r="J32" t="n">
-        <v>281.67</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1165684</v>
-      </c>
-      <c r="L32" t="n">
-        <v>50298520</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>log6214</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>13162843312</v>
-      </c>
-      <c r="C33" t="n">
-        <v>9592469</v>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="n">
-        <v>14526602521</v>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="n">
-        <v>200735635649</v>
-      </c>
-      <c r="H33" t="n">
-        <v>1016592873175</v>
-      </c>
-      <c r="I33" t="n">
-        <v>2320</v>
-      </c>
-      <c r="J33" t="n">
-        <v>281.67</v>
-      </c>
-      <c r="K33" t="n">
-        <v>1165684</v>
-      </c>
-      <c r="L33" t="n">
-        <v>47038773.67</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>log6314</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>12991075469</v>
-      </c>
-      <c r="C34" t="n">
-        <v>9603997</v>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="n">
-        <v>14164770714</v>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="n">
-        <v>119294443318</v>
-      </c>
-      <c r="H34" t="n">
-        <v>911650972138</v>
-      </c>
-      <c r="I34" t="n">
-        <v>86144</v>
-      </c>
-      <c r="J34" t="n">
-        <v>233.67</v>
-      </c>
-      <c r="K34" t="n">
-        <v>966724</v>
-      </c>
-      <c r="L34" t="n">
-        <v>39096797.67</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>log6414</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>13009149098</v>
-      </c>
-      <c r="C35" t="n">
-        <v>9540457</v>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="n">
-        <v>13611392919</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="n">
-        <v>720437553</v>
-      </c>
-      <c r="H35" t="n">
-        <v>791450427366</v>
-      </c>
-      <c r="I35" t="n">
-        <v>155488</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>log6514</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>13401427720</v>
-      </c>
-      <c r="C36" t="n">
-        <v>9529830</v>
-      </c>
-      <c r="D36" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E36" t="n">
-        <v>14788106340</v>
-      </c>
-      <c r="F36" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G36" t="n">
-        <v>201833805235</v>
-      </c>
-      <c r="H36" t="n">
-        <v>992586427127</v>
-      </c>
-      <c r="I36" t="n">
-        <v>2098</v>
-      </c>
-      <c r="J36" t="n">
-        <v>281.67</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1165684</v>
-      </c>
-      <c r="L36" t="n">
-        <v>47897023.67</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>log6614</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>13107116106</v>
-      </c>
-      <c r="C37" t="n">
-        <v>9551217</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="n">
-        <v>14878175283</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>141432066254</v>
-      </c>
-      <c r="H37" t="n">
-        <v>928705019419</v>
-      </c>
-      <c r="I37" t="n">
-        <v>14258</v>
-      </c>
-      <c r="J37" t="n">
-        <v>246.67</v>
-      </c>
-      <c r="K37" t="n">
-        <v>1021354</v>
-      </c>
-      <c r="L37" t="n">
-        <v>42271371.67</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>log6714</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>13002801521</v>
-      </c>
-      <c r="C38" t="n">
-        <v>9517341</v>
-      </c>
-      <c r="D38" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E38" t="n">
-        <v>13103652760</v>
-      </c>
-      <c r="F38" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G38" t="n">
-        <v>195942643712</v>
-      </c>
-      <c r="H38" t="n">
-        <v>981737149572</v>
-      </c>
-      <c r="I38" t="n">
-        <v>1361</v>
-      </c>
-      <c r="J38" t="n">
-        <v>281.67</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1165684</v>
-      </c>
-      <c r="L38" t="n">
-        <v>43876768.67</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>log6814</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>13045007458</v>
-      </c>
-      <c r="C39" t="n">
-        <v>9596328</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="E39" t="n">
-        <v>14563017682</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.0372</v>
-      </c>
-      <c r="G39" t="n">
-        <v>157527662069</v>
-      </c>
-      <c r="H39" t="n">
-        <v>947114060265</v>
-      </c>
-      <c r="I39" t="n">
-        <v>5326</v>
-      </c>
-      <c r="J39" t="n">
-        <v>263</v>
-      </c>
-      <c r="K39" t="n">
-        <v>1087212.33</v>
-      </c>
-      <c r="L39" t="n">
-        <v>44045501</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>log6914</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>13289891129</v>
-      </c>
-      <c r="C40" t="n">
-        <v>9248700</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E40" t="n">
-        <v>14723761840</v>
-      </c>
-      <c r="F40" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G40" t="n">
-        <v>203326804337</v>
-      </c>
-      <c r="H40" t="n">
-        <v>992222658329</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1730</v>
-      </c>
-      <c r="J40" t="n">
-        <v>281.67</v>
-      </c>
-      <c r="K40" t="n">
-        <v>1165684</v>
-      </c>
-      <c r="L40" t="n">
-        <v>45897708.33</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>log7014</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>13354707712</v>
-      </c>
-      <c r="C41" t="n">
-        <v>9722088</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0.0035</v>
-      </c>
-      <c r="E41" t="n">
-        <v>14764837744</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.0007</v>
-      </c>
-      <c r="G41" t="n">
-        <v>142245242677</v>
-      </c>
-      <c r="H41" t="n">
-        <v>932105944845</v>
-      </c>
-      <c r="I41" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J41" t="n">
-        <v>247.67</v>
-      </c>
-      <c r="K41" t="n">
-        <v>1025558</v>
-      </c>
-      <c r="L41" t="n">
-        <v>41295446</v>
-      </c>
+        <v>5549</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
